--- a/Planejamento_Horus.xlsx
+++ b/Planejamento_Horus.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mshimizu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fesantos\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="25">
   <si>
     <t>Mateus</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Em Andamento</t>
-  </si>
-  <si>
-    <t>Pendente</t>
   </si>
   <si>
     <t>Visualizador Dados</t>
@@ -100,13 +97,16 @@
   <si>
     <t>Hora Conclusão</t>
   </si>
+  <si>
+    <t>Gerar relatorio de analise de IA nos fontes do sistema cidade legal</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -180,8 +180,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -482,16 +485,16 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
@@ -518,7 +521,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="7"/>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
@@ -539,10 +542,10 @@
       <c r="D3" s="1"/>
       <c r="E3" s="7"/>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>0</v>
@@ -557,19 +560,23 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.43263888888888885</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -578,136 +585,154 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="7"/>
+      <c r="D5" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.56388888888888888</v>
+      </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="1">
+        <v>46098</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.71250000000000002</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="7"/>
+      <c r="D7" s="1">
+        <v>46099</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.75</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="7"/>
+      <c r="D8" s="1">
+        <v>46099</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.49861111111111112</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="1">
+        <v>46100</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.49652777777777773</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="H9" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46098</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="1"/>
       <c r="E10" s="7"/>
       <c r="F10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46098</v>
-      </c>
+      <c r="A11" s="4"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
       <c r="D11" s="1"/>
       <c r="E11" s="7"/>
       <c r="F11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>8</v>
@@ -720,11 +745,11 @@
       <c r="D12" s="1"/>
       <c r="E12" s="7"/>
       <c r="F12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -737,11 +762,11 @@
       <c r="D13" s="1"/>
       <c r="E13" s="7"/>
       <c r="F13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>8</v>
@@ -754,11 +779,11 @@
       <c r="D14" s="1"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -771,11 +796,11 @@
       <c r="D15" s="1"/>
       <c r="E15" s="7"/>
       <c r="F15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>8</v>
@@ -788,11 +813,11 @@
       <c r="D16" s="1"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>8</v>
@@ -805,11 +830,11 @@
       <c r="D17" s="1"/>
       <c r="E17" s="7"/>
       <c r="F17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>8</v>
@@ -822,11 +847,11 @@
       <c r="D18" s="1"/>
       <c r="E18" s="7"/>
       <c r="F18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>8</v>
@@ -839,11 +864,11 @@
       <c r="D19" s="1"/>
       <c r="E19" s="7"/>
       <c r="F19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>8</v>
@@ -856,11 +881,11 @@
       <c r="D20" s="1"/>
       <c r="E20" s="7"/>
       <c r="F20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
@@ -873,11 +898,11 @@
       <c r="D21" s="1"/>
       <c r="E21" s="7"/>
       <c r="F21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>8</v>
@@ -890,11 +915,11 @@
       <c r="D22" s="1"/>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
@@ -907,11 +932,11 @@
       <c r="D23" s="1"/>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>8</v>
@@ -924,11 +949,11 @@
       <c r="D24" s="1"/>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>8</v>
@@ -941,11 +966,11 @@
       <c r="D25" s="1"/>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>8</v>
@@ -958,11 +983,11 @@
       <c r="D26" s="1"/>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>8</v>
@@ -975,11 +1000,11 @@
       <c r="D27" s="1"/>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>8</v>
@@ -992,11 +1017,11 @@
       <c r="D28" s="1"/>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>8</v>
@@ -1009,11 +1034,11 @@
       <c r="D29" s="1"/>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>8</v>
@@ -1026,11 +1051,11 @@
       <c r="D30" s="1"/>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>8</v>
@@ -1043,11 +1068,11 @@
       <c r="D31" s="1"/>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>8</v>
@@ -1060,11 +1085,11 @@
       <c r="D32" s="1"/>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
@@ -1077,11 +1102,11 @@
       <c r="D33" s="1"/>
       <c r="E33" s="7"/>
       <c r="F33" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>8</v>
@@ -1094,11 +1119,11 @@
       <c r="D34" s="1"/>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>8</v>
@@ -1111,11 +1136,11 @@
       <c r="D35" s="1"/>
       <c r="E35" s="7"/>
       <c r="F35" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>8</v>
@@ -1128,11 +1153,11 @@
       <c r="D36" s="1"/>
       <c r="E36" s="7"/>
       <c r="F36" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>8</v>
@@ -1145,11 +1170,11 @@
       <c r="D37" s="1"/>
       <c r="E37" s="7"/>
       <c r="F37" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>8</v>
@@ -1162,11 +1187,11 @@
       <c r="D38" s="1"/>
       <c r="E38" s="7"/>
       <c r="F38" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>8</v>
@@ -1179,11 +1204,11 @@
       <c r="D39" s="1"/>
       <c r="E39" s="7"/>
       <c r="F39" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>8</v>
@@ -1196,11 +1221,11 @@
       <c r="D40" s="1"/>
       <c r="E40" s="7"/>
       <c r="F40" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>8</v>
@@ -1213,11 +1238,11 @@
       <c r="D41" s="1"/>
       <c r="E41" s="7"/>
       <c r="F41" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>8</v>
@@ -1230,11 +1255,11 @@
       <c r="D42" s="1"/>
       <c r="E42" s="7"/>
       <c r="F42" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -1247,11 +1272,11 @@
       <c r="D43" s="1"/>
       <c r="E43" s="7"/>
       <c r="F43" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
@@ -1264,11 +1289,11 @@
       <c r="D44" s="1"/>
       <c r="E44" s="7"/>
       <c r="F44" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
@@ -1281,11 +1306,11 @@
       <c r="D45" s="1"/>
       <c r="E45" s="7"/>
       <c r="F45" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -1298,11 +1323,11 @@
       <c r="D46" s="1"/>
       <c r="E46" s="7"/>
       <c r="F46" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>8</v>
@@ -1315,11 +1340,11 @@
       <c r="D47" s="1"/>
       <c r="E47" s="7"/>
       <c r="F47" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -1332,11 +1357,11 @@
       <c r="D48" s="1"/>
       <c r="E48" s="7"/>
       <c r="F48" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
@@ -1349,11 +1374,11 @@
       <c r="D49" s="1"/>
       <c r="E49" s="7"/>
       <c r="F49" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>8</v>
@@ -1366,11 +1391,11 @@
       <c r="D50" s="1"/>
       <c r="E50" s="7"/>
       <c r="F50" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>8</v>
@@ -1383,11 +1408,11 @@
       <c r="D51" s="1"/>
       <c r="E51" s="7"/>
       <c r="F51" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>8</v>
@@ -1400,11 +1425,11 @@
       <c r="D52" s="1"/>
       <c r="E52" s="7"/>
       <c r="F52" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
@@ -1417,11 +1442,11 @@
       <c r="D53" s="1"/>
       <c r="E53" s="7"/>
       <c r="F53" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>8</v>
@@ -1434,11 +1459,11 @@
       <c r="D54" s="1"/>
       <c r="E54" s="7"/>
       <c r="F54" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>8</v>
@@ -1451,11 +1476,11 @@
       <c r="D55" s="1"/>
       <c r="E55" s="7"/>
       <c r="F55" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>8</v>
@@ -1468,11 +1493,11 @@
       <c r="D56" s="1"/>
       <c r="E56" s="7"/>
       <c r="F56" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>8</v>
@@ -1485,11 +1510,11 @@
       <c r="D57" s="1"/>
       <c r="E57" s="7"/>
       <c r="F57" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
@@ -1502,11 +1527,11 @@
       <c r="D58" s="1"/>
       <c r="E58" s="7"/>
       <c r="F58" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
@@ -1519,11 +1544,11 @@
       <c r="D59" s="1"/>
       <c r="E59" s="7"/>
       <c r="F59" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
@@ -1536,11 +1561,11 @@
       <c r="D60" s="1"/>
       <c r="E60" s="7"/>
       <c r="F60" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>8</v>
@@ -1553,11 +1578,11 @@
       <c r="D61" s="1"/>
       <c r="E61" s="7"/>
       <c r="F61" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>8</v>
@@ -1570,11 +1595,11 @@
       <c r="D62" s="1"/>
       <c r="E62" s="7"/>
       <c r="F62" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
@@ -1587,11 +1612,11 @@
       <c r="D63" s="1"/>
       <c r="E63" s="7"/>
       <c r="F63" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>8</v>
@@ -1604,11 +1629,11 @@
       <c r="D64" s="1"/>
       <c r="E64" s="7"/>
       <c r="F64" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>8</v>
@@ -1621,11 +1646,11 @@
       <c r="D65" s="1"/>
       <c r="E65" s="7"/>
       <c r="F65" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>8</v>
@@ -1638,11 +1663,11 @@
       <c r="D66" s="1"/>
       <c r="E66" s="7"/>
       <c r="F66" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>8</v>
@@ -1655,11 +1680,11 @@
       <c r="D67" s="1"/>
       <c r="E67" s="7"/>
       <c r="F67" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>8</v>
@@ -1672,11 +1697,11 @@
       <c r="D68" s="1"/>
       <c r="E68" s="7"/>
       <c r="F68" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>8</v>
@@ -1689,11 +1714,11 @@
       <c r="D69" s="1"/>
       <c r="E69" s="7"/>
       <c r="F69" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>8</v>
@@ -1706,11 +1731,11 @@
       <c r="D70" s="1"/>
       <c r="E70" s="7"/>
       <c r="F70" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>8</v>
@@ -1723,11 +1748,11 @@
       <c r="D71" s="1"/>
       <c r="E71" s="7"/>
       <c r="F71" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>8</v>
@@ -1740,11 +1765,11 @@
       <c r="D72" s="1"/>
       <c r="E72" s="7"/>
       <c r="F72" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
@@ -1757,11 +1782,11 @@
       <c r="D73" s="1"/>
       <c r="E73" s="7"/>
       <c r="F73" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>8</v>
@@ -1774,11 +1799,11 @@
       <c r="D74" s="1"/>
       <c r="E74" s="7"/>
       <c r="F74" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>8</v>
@@ -1791,11 +1816,11 @@
       <c r="D75" s="1"/>
       <c r="E75" s="7"/>
       <c r="F75" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>8</v>
@@ -1808,11 +1833,11 @@
       <c r="D76" s="1"/>
       <c r="E76" s="7"/>
       <c r="F76" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>8</v>
@@ -1825,11 +1850,11 @@
       <c r="D77" s="1"/>
       <c r="E77" s="7"/>
       <c r="F77" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>8</v>
@@ -1842,11 +1867,11 @@
       <c r="D78" s="1"/>
       <c r="E78" s="7"/>
       <c r="F78" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>8</v>
@@ -1859,11 +1884,11 @@
       <c r="D79" s="1"/>
       <c r="E79" s="7"/>
       <c r="F79" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>8</v>
@@ -1876,11 +1901,11 @@
       <c r="D80" s="1"/>
       <c r="E80" s="7"/>
       <c r="F80" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>8</v>
@@ -1893,11 +1918,11 @@
       <c r="D81" s="1"/>
       <c r="E81" s="7"/>
       <c r="F81" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>8</v>
@@ -1910,11 +1935,11 @@
       <c r="D82" s="1"/>
       <c r="E82" s="7"/>
       <c r="F82" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>8</v>
@@ -1927,11 +1952,11 @@
       <c r="D83" s="1"/>
       <c r="E83" s="7"/>
       <c r="F83" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
@@ -1944,11 +1969,11 @@
       <c r="D84" s="1"/>
       <c r="E84" s="7"/>
       <c r="F84" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>8</v>
@@ -1961,11 +1986,11 @@
       <c r="D85" s="1"/>
       <c r="E85" s="7"/>
       <c r="F85" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>8</v>
@@ -1978,11 +2003,11 @@
       <c r="D86" s="1"/>
       <c r="E86" s="7"/>
       <c r="F86" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>8</v>
@@ -1995,11 +2020,11 @@
       <c r="D87" s="1"/>
       <c r="E87" s="7"/>
       <c r="F87" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>8</v>
@@ -2012,11 +2037,11 @@
       <c r="D88" s="1"/>
       <c r="E88" s="7"/>
       <c r="F88" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>8</v>
@@ -2029,11 +2054,11 @@
       <c r="D89" s="1"/>
       <c r="E89" s="7"/>
       <c r="F89" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>8</v>
@@ -2046,11 +2071,11 @@
       <c r="D90" s="1"/>
       <c r="E90" s="7"/>
       <c r="F90" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>8</v>
@@ -2063,11 +2088,11 @@
       <c r="D91" s="1"/>
       <c r="E91" s="7"/>
       <c r="F91" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
@@ -2080,11 +2105,11 @@
       <c r="D92" s="1"/>
       <c r="E92" s="7"/>
       <c r="F92" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>8</v>
@@ -2097,11 +2122,11 @@
       <c r="D93" s="1"/>
       <c r="E93" s="7"/>
       <c r="F93" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>8</v>
@@ -2114,11 +2139,11 @@
       <c r="D94" s="1"/>
       <c r="E94" s="7"/>
       <c r="F94" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
@@ -2131,11 +2156,11 @@
       <c r="D95" s="1"/>
       <c r="E95" s="7"/>
       <c r="F95" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>8</v>
@@ -2148,11 +2173,11 @@
       <c r="D96" s="1"/>
       <c r="E96" s="7"/>
       <c r="F96" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
@@ -2165,11 +2190,11 @@
       <c r="D97" s="1"/>
       <c r="E97" s="7"/>
       <c r="F97" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>8</v>
@@ -2182,11 +2207,11 @@
       <c r="D98" s="1"/>
       <c r="E98" s="7"/>
       <c r="F98" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>8</v>
@@ -2199,11 +2224,11 @@
       <c r="D99" s="1"/>
       <c r="E99" s="7"/>
       <c r="F99" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>8</v>
@@ -2216,11 +2241,11 @@
       <c r="D100" s="1"/>
       <c r="E100" s="7"/>
       <c r="F100" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>8</v>
@@ -2233,11 +2258,11 @@
       <c r="D101" s="1"/>
       <c r="E101" s="7"/>
       <c r="F101" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>
@@ -2250,11 +2275,11 @@
       <c r="D102" s="1"/>
       <c r="E102" s="7"/>
       <c r="F102" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>8</v>
@@ -2267,11 +2292,11 @@
       <c r="D103" s="1"/>
       <c r="E103" s="7"/>
       <c r="F103" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>8</v>
@@ -2284,11 +2309,11 @@
       <c r="D104" s="1"/>
       <c r="E104" s="7"/>
       <c r="F104" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>8</v>
@@ -2301,11 +2326,11 @@
       <c r="D105" s="1"/>
       <c r="E105" s="7"/>
       <c r="F105" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>8</v>
@@ -2318,11 +2343,11 @@
       <c r="D106" s="1"/>
       <c r="E106" s="7"/>
       <c r="F106" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>8</v>
@@ -2335,11 +2360,11 @@
       <c r="D107" s="1"/>
       <c r="E107" s="7"/>
       <c r="F107" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>8</v>
@@ -2352,11 +2377,11 @@
       <c r="D108" s="1"/>
       <c r="E108" s="7"/>
       <c r="F108" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>8</v>
@@ -2369,11 +2394,11 @@
       <c r="D109" s="1"/>
       <c r="E109" s="7"/>
       <c r="F109" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>8</v>
@@ -2386,11 +2411,11 @@
       <c r="D110" s="1"/>
       <c r="E110" s="7"/>
       <c r="F110" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>8</v>
@@ -2403,11 +2428,11 @@
       <c r="D111" s="1"/>
       <c r="E111" s="7"/>
       <c r="F111" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>8</v>
@@ -2420,11 +2445,11 @@
       <c r="D112" s="1"/>
       <c r="E112" s="7"/>
       <c r="F112" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>8</v>
@@ -2437,11 +2462,11 @@
       <c r="D113" s="1"/>
       <c r="E113" s="7"/>
       <c r="F113" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>8</v>
@@ -2454,11 +2479,11 @@
       <c r="D114" s="1"/>
       <c r="E114" s="7"/>
       <c r="F114" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>8</v>
@@ -2471,11 +2496,11 @@
       <c r="D115" s="1"/>
       <c r="E115" s="7"/>
       <c r="F115" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>8</v>
@@ -2488,11 +2513,11 @@
       <c r="D116" s="1"/>
       <c r="E116" s="7"/>
       <c r="F116" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>8</v>
@@ -2505,11 +2530,11 @@
       <c r="D117" s="1"/>
       <c r="E117" s="7"/>
       <c r="F117" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>8</v>
@@ -2522,11 +2547,11 @@
       <c r="D118" s="1"/>
       <c r="E118" s="7"/>
       <c r="F118" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>8</v>
@@ -2539,11 +2564,11 @@
       <c r="D119" s="1"/>
       <c r="E119" s="7"/>
       <c r="F119" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>8</v>
@@ -2556,80 +2581,29 @@
       <c r="D120" s="1"/>
       <c r="E120" s="7"/>
       <c r="F120" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G121" s="4"/>
-      <c r="H121" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G122" s="4"/>
-      <c r="H122" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" s="4"/>
-      <c r="H123" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I123" s="3" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B11">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B9">
       <formula1>46098</formula1>
       <formula2>46101</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I123">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I120">
       <formula1>"Iniciado,Pendente,Em Andamento,Concluido,Atrasado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H123">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H120">
       <formula1>"Fernando,Mateus,Ana,Ricardo,Masa,Viviane"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F123">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F120">
       <formula1>"Urgente,Alta,Media,Baixa"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Planejamento_Horus.xlsx
+++ b/Planejamento_Horus.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fesantos\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fesantos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="26">
   <si>
     <t>Mateus</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Urgente</t>
   </si>
   <si>
-    <t>Restore do Database Cidade Legal no Servidor</t>
-  </si>
-  <si>
     <t>Pedido de Backup de Produção</t>
   </si>
   <si>
@@ -99,6 +96,12 @@
   </si>
   <si>
     <t>Gerar relatorio de analise de IA nos fontes do sistema cidade legal</t>
+  </si>
+  <si>
+    <t>Publicação do Sistema Cidade Legal no novo servidor srvweb2</t>
+  </si>
+  <si>
+    <t>Restore do Database Cidade Legal no novo servidor srvweb2</t>
   </si>
 </sst>
 </file>
@@ -485,16 +488,16 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
@@ -645,7 +648,7 @@
         <v>15</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>10</v>
@@ -670,10 +673,10 @@
         <v>16</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
@@ -695,7 +698,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>10</v>
@@ -704,16 +707,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46101</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="1">
+        <v>46101</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.75</v>
+      </c>
       <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="H10" s="5" t="s">
         <v>10</v>
       </c>
